--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>10/08 13:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>09/08 20:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>70</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>10/08 09:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>11/08 22:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>07/08 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>10/08 00:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>08/08 15:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>10/08 18:15</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>45</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>10/08 17:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>35</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>09/08 10:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>35</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>09/08 00:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>06/08 02:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>20</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>09/08 15:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>06/08 00:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>20</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>05/08 17:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
+      <c r="F25" t="n">
+        <v>1.09</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45874.08541881981</v>
+        <v>45874.08541881944</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Alex De Mi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alex De Minaur – Ben SheltonATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06/08 00:10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45874.17328188645</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fenerbahce – AlanyasporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+2,11%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45874.17328188645</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 11-2- se qualifie | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ludogorets Razgrad – Ferencvárosi TCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>06/08 17:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+2,03%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45874.17328188645</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Malmö – Co</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Malmö – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>05/08 17:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+0,32%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45874.17328188645</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>06/08 00:10</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
+      <c r="F27" t="n">
+        <v>5.4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45874.17328188645</v>
+        <v>45874.17328188657</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45874.17328188645</v>
+        <v>45874.17328188657</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>06/08 17:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.35</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45874.17328188645</v>
+        <v>45874.17328188657</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>05/08 17:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2.75</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45874.17328188645</v>
+        <v>45874.17328188657</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | KFC Komarn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KFC Komarno – Slovan BratislavaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/08 16:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+0,46%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45874.23055188419</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>09/08 16:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>35</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,142 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45874.23055188419</v>
+        <v>45874.23055188658</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Shkendi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FK Shkendija – Qarabag FKLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45874.27625826362</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HNK Rijeka – Shelbourne FCLigue Europa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>06/08 18:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+0,87%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45874.27625826362</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21-2- se qualifie | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – FC Viktoria PlzenEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05/08 18:45</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>50,2%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+0,33%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45874.27625826362</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -1795,10 +1795,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>50</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45874.27625826362</v>
+        <v>45874.27625826389</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>06/08 18:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45874.27625826362</v>
+        <v>45874.27625826389</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>05/08 18:45</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45874.27625826362</v>
+        <v>45874.27625826389</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +1898,141 @@
         <v>45874.27625826389</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Vikingur G</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Vikingur Gota – LinfieldLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+6,77%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45874.35672876278</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Beach volley | 21-2 | Luini / Po</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Luini / Poiesz – Windeleff / BisgaardBaden Challenge F.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>05/08 09:40</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+3,50%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45874.35672876278</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Etoile Rouge BelgradeEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06/08 18:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+3,03%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45874.35672876278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>17</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45874.35672876278</v>
+        <v>45874.35672876157</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>05/08 09:40</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
+      <c r="F36" t="n">
+        <v>4.7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45874.35672876278</v>
+        <v>45874.35672876157</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>06/08 18:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1.8</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,277 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45874.35672876278</v>
+        <v>45874.35672876157</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – FC Viktoria PlzenEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05/08 18:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45874.39597609918</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 24.5 - tirs | KF Shkëndi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>KF Shkëndija – Qarabag AgdamEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>50,4%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+10,8%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45874.39597609918</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 7.5 - tirs2e équipe | Dynamo Kie</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dynamo Kiev – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+5,02%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45874.39597609918</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21-2- se qualifie | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ludogorets Razgrad – Ferencvárosi TCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06/08 17:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>60,2%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+3,56%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45874.39597609918</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Beach volley | 21-2 | K.Elsner /</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>K.Elsner / J.Pfau – M.Bentele / A.NiederhauserChallenge - Baden (F)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>05/08 09:40</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+3,54%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45874.39597609918</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21-2- se qualifie | Polissya Z</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Polissya Zhytomyr – Paksi SEEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>49,9%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+2,38%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45874.39597609918</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>05/08 18:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2.33</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45874.39597609918</v>
+        <v>45874.39597609953</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45874.39597609918</v>
+        <v>45874.39597609953</v>
       </c>
     </row>
     <row r="40">
@@ -2143,10 +2139,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2159,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45874.39597609918</v>
+        <v>45874.39597609953</v>
       </c>
     </row>
     <row r="41">
@@ -2188,10 +2182,8 @@
           <t>06/08 17:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F41" t="n">
+        <v>1.72</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2204,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45874.39597609918</v>
+        <v>45874.39597609953</v>
       </c>
     </row>
     <row r="42">
@@ -2233,10 +2225,8 @@
           <t>05/08 09:40</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2249,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45874.39597609918</v>
+        <v>45874.39597609953</v>
       </c>
     </row>
     <row r="43">
@@ -2278,10 +2268,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.05</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2294,7 +2282,142 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45874.39597609918</v>
+        <v>45874.39597609953</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Klaksvik –</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Klaksvik – Neman GrodnoEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05/08 18:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+31,7%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45874.43556494559</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 27.5 - tirs | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Viktoria PlzenEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>05/08 18:45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>57,1%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+8,44%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45874.43556494559</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Beach volley | 21-2 | Dvornikova</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dvornikova / Zolnercikova – Fejes / FlemingBaden Challenge F.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>05/08 12:10</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+4,65%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45874.43556494559</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>05/08 18:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.53</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45874.43556494559</v>
+        <v>45874.43556494213</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>05/08 18:45</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F45" t="n">
+        <v>1.9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45874.43556494559</v>
+        <v>45874.43556494213</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>05/08 12:10</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.97</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,232 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45874.43556494559</v>
+        <v>45874.43556494213</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – TSC Backa TopolaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>09/08 18:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+40,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45874.47352741245</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Napreda</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FK Napredak – Partizan BelgradeSuperLiga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10/08 18:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45874.47352741245</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 13.5 - tirs1re équipe | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Viktoria PlzenEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>05/08 18:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>50,2%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45874.47352741245</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Plus que 24.5 | Krawietz K</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Krawietz K / Puetz T – Cash J / Glasspool LEvénements. ATP Toronto Double</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 24.5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>05/08 20:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>18,6%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+7,80%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45874.47352741245</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spartak Su</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spartak Subotica – Mladost LucaniSuperLiga</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>09/08 18:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+4,80%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45874.47352741245</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45874.47352741245</v>
+        <v>45874.4735274074</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>10/08 18:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>40</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45874.47352741245</v>
+        <v>45874.4735274074</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>05/08 18:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45874.47352741245</v>
+        <v>45874.4735274074</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2569,8 @@
           <t>05/08 20:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>5.80</t>
-        </is>
+      <c r="F50" t="n">
+        <v>5.8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2591,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45874.47352741245</v>
+        <v>45874.4735274074</v>
       </c>
     </row>
     <row r="51">
@@ -2620,10 +2612,8 @@
           <t>09/08 18:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2636,7 +2626,322 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45874.47352741245</v>
+        <v>45874.4735274074</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | SCU Torree</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SCU Torreense – Sporting Lisbon BPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>09/08 13:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+58,5%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45874.5366276133</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Javor Ivan</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica – Radnicki KragujevacSuperLiga</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>11/08 17:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+33,7%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45874.5366276133</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 14.5 - tirs2e équipe | KF Shkëndi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>KF Shkëndija – Qarabag AgdamEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+19,7%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45874.5366276133</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CFR Cluj –</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CFR Cluj – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>07/08 16:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+5,95%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45874.5366276133</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 10.5 - tir cadré | Feyenoord </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Feyenoord – FenerbahçeEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06/08 19:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+5,44%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45874.5366276133</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS Maritim</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CS Maritimo – Lusitania FC LourosaPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10/08 13:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+4,68%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45874.5366276133</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Etoile Rouge BelgradeEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>06/08 18:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+4,35%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45874.5366276133</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>09/08 13:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>55</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>11/08 17:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>50</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2.3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
       </c>
     </row>
     <row r="55">
@@ -2790,10 +2784,8 @@
           <t>07/08 16:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2806,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
       </c>
     </row>
     <row r="56">
@@ -2835,10 +2827,8 @@
           <t>06/08 19:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2851,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
       </c>
     </row>
     <row r="57">
@@ -2880,10 +2870,8 @@
           <t>10/08 13:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>35</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2896,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
       </c>
     </row>
     <row r="58">
@@ -2925,10 +2913,8 @@
           <t>06/08 18:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F58" t="n">
+        <v>1.95</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2941,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45874.5366276133</v>
+        <v>45874.53662761574</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Botosan</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FC Botosani – FC Arges PitestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>11/08 16:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45874.57199946923</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 - tir cadré2e équipe | Nice – Ben</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Nice – BenficaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06/08 19:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+5,92%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45874.57199946923</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>11/08 16:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>50</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45874.57199946923</v>
+        <v>45874.57199946759</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>06/08 19:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F60" t="n">
+        <v>2.55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,52 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45874.57199946923</v>
+        <v>45874.57199946759</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 - tir cadré2e équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Etoile Rouge BelgradeLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06/08 18:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+11,2%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45874.60272373075</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>06/08 18:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.8</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,52 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45874.60272373075</v>
+        <v>45874.60272372685</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Plus que 6.51er set1er participant | Alexander </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Alexander Zverev – Karen KhachanovATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>06/08 20:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+1,33%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45874.64456254822</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>06/08 20:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
+      <c r="F62" t="n">
+        <v>4.9</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,97 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45874.64456254822</v>
+        <v>45874.64456254629</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 15.5 - tirs2e équipe | Shkendija </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Shkendija Tetovo – QarabağEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 15.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>58,8%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+12,4%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45874.68466311708</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 5.5 - tir cadré1re équipe | Feyenoord </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Feyenoord – FenerbahceEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>06/08 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+4,31%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45874.68466311708</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="F63" t="n">
+        <v>1.91</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45874.68466311708</v>
+        <v>45874.68466311342</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>06/08 19:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2.2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,142 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45874.68466311708</v>
+        <v>45874.68466311342</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Madison Ke</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Madison Keys – Clara TausonWTA - Montréal</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>05/08 22:05</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+4,78%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45874.72418077322</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CA Tigre – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08/08 22:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+2,93%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45874.72418077322</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs2e équipe | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – FC Viktoria PlzenEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>05/08 18:45</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>54,4%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+1,67%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45874.72418077322</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>05/08 22:05</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.55</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45874.72418077322</v>
+        <v>45874.72418077546</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>08/08 22:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>45</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45874.72418077322</v>
+        <v>45874.72418077546</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>05/08 18:45</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
+      <c r="F67" t="n">
+        <v>1.87</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,142 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45874.72418077322</v>
+        <v>45874.72418077546</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Sport</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Club Sportivo Luqueno – CA Tembetary YpanePrimera Division</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>09/08 21:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+7,73%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45874.77605714411</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 11-2- se qualifie | Differdang</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Differdange 03 – FC Levadia TallinnEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+3,83%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45874.77605714411</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Burgos CF </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Burgos CF – Cult. LeonesaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>15/08 17:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+2,54%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45874.77605714411</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>09/08 21:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>40</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45874.77605714411</v>
+        <v>45874.77605714121</v>
       </c>
     </row>
     <row r="69">
@@ -3388,10 +3386,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
+      <c r="F69" t="n">
+        <v>2.37</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3404,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45874.77605714411</v>
+        <v>45874.77605714121</v>
       </c>
     </row>
     <row r="70">
@@ -3433,10 +3429,8 @@
           <t>15/08 17:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>50</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3449,7 +3443,187 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45874.77605714411</v>
+        <v>45874.77605714121</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tirs2e équipe | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Anderlecht – Sheriff TiraspolEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>07/08 18:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>67,7%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45874.80813509883</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Volleyball | Moins que 3.5 | Grèce F – </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Grèce F – Autriche FMonde - Euro QF</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>06/08 17:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+8,24%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45874.80813509883</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball | Moins que 3.5 | Israël F –</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Israël F – Slovénie FMonde - Euro QF</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>06/08 18:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+6,37%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45874.80813509883</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Volleyball | Moins que 3.5 | Allemagne </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Allemagne F – Suisse FMonde - Euro QF</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>06/08 17:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+3,39%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45874.80813509883</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -3472,10 +3472,8 @@
           <t>07/08 18:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F71" t="n">
+        <v>1.72</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45874.80813509883</v>
+        <v>45874.80813510417</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>06/08 17:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
+      <c r="F72" t="n">
+        <v>1.29</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45874.80813509883</v>
+        <v>45874.80813510417</v>
       </c>
     </row>
     <row r="73">
@@ -3562,10 +3558,8 @@
           <t>06/08 18:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="F73" t="n">
+        <v>1.33</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45874.80813509883</v>
+        <v>45874.80813510417</v>
       </c>
     </row>
     <row r="74">
@@ -3607,10 +3601,8 @@
           <t>06/08 17:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
+      <c r="F74" t="n">
+        <v>1.34</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3623,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45874.80813509883</v>
+        <v>45874.80813510417</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,6 +3618,51 @@
         <v>45874.80813510417</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 10.5 - tir cadré | Nice – Ben</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Nice – BenficaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>06/08 19:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>39,5%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+4,54%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45874.93373978124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-05.xlsx
+++ b/data/valuebets_database_2025-08-05.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,10 +3644,8 @@
           <t>06/08 19:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F75" t="n">
+        <v>2.65</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,97 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45874.93373978124</v>
+        <v>45874.93373978009</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | 1 | CF Montréa</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CF Montréal – Club PueblaLeagues Cup</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>06/08 00:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>52,1%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+7,41%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45874.9748936791</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | EC Bahia –</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EC Bahia – FluminenseSérie A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>10/08 00:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+4,83%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45874.9748936791</v>
       </c>
     </row>
   </sheetData>
